--- a/查询表.xlsx
+++ b/查询表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\张天夫\Documents\MATLAB\Transfer-learning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76AE1F53-18C7-4F31-86C1-445989EA9F64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB9FA103-6FB6-41A0-A448-80ADFD491CB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="20" activeTab="31" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="20" activeTab="32" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="声光PCA" sheetId="39" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="803" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="79">
   <si>
     <t>GroupName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -347,10 +347,6 @@
   </si>
   <si>
     <t>Learned</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Learned,Transfer</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -3128,7 +3124,7 @@
         <v>71</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>70</v>
@@ -3140,13 +3136,13 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>73</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>74</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>64</v>
@@ -3299,16 +3295,15 @@
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8056A83F-BC10-47F4-9E5B-271761E7A9D3}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.625" customWidth="1"/>
     <col min="2" max="2" width="30.625" customWidth="1"/>
-    <col min="3" max="3" width="10.625" customWidth="1"/>
-    <col min="5" max="5" width="20.625" customWidth="1"/>
+    <col min="3" max="4" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3322,13 +3317,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>45</v>
       </c>
@@ -3339,16 +3331,13 @@
         <v>8</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+        <v>64</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>46</v>
       </c>
@@ -3359,41 +3348,34 @@
         <v>8</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+        <v>64</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+        <v>64</v>
+      </c>
+      <c r="E4" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3429,7 +3411,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>2</v>
@@ -3444,7 +3426,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>2</v>
@@ -3459,7 +3441,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>2</v>
@@ -3474,7 +3456,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>11</v>
@@ -3488,7 +3470,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -3646,16 +3628,15 @@
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFFD7975-4DBD-40DC-99B8-46C75232DDD3}">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.625" customWidth="1"/>
     <col min="2" max="2" width="30.625" customWidth="1"/>
-    <col min="4" max="4" width="10.625" customWidth="1"/>
-    <col min="5" max="5" width="20.625" customWidth="1"/>
+    <col min="3" max="4" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3669,31 +3650,25 @@
         <v>5</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" s="1"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="E2" s="1"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>33</v>
       </c>
@@ -3701,19 +3676,16 @@
         <v>9</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="E3" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>34</v>
       </c>
@@ -3721,31 +3693,28 @@
         <v>9</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="E4" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
     </row>
   </sheetData>

--- a/查询表.xlsx
+++ b/查询表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\张天夫\Documents\MATLAB\Transfer-learning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB9FA103-6FB6-41A0-A448-80ADFD491CB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6269AA69-730E-4554-8246-B07EC8D6C9C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="20" activeTab="32" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="16" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="声光PCA" sheetId="39" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="84">
   <si>
     <t>GroupName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -375,6 +375,26 @@
   </si>
   <si>
     <t>transfer_LightWater</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AudioWater_First</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AudioWater_Last</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TrialRI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16:20</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2107,7 +2127,7 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="20.625" customWidth="1"/>
-    <col min="3" max="3" width="10.625" customWidth="1"/>
+    <col min="3" max="4" width="10.625" customWidth="1"/>
     <col min="5" max="5" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2125,49 +2145,57 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>23</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="E2" s="3"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>23</v>
+        <v>64</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
+      <c r="A4" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>83</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/查询表.xlsx
+++ b/查询表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\张天夫\Documents\MATLAB\Transfer-learning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6269AA69-730E-4554-8246-B07EC8D6C9C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{102598FF-C6A1-4613-A563-FD5BC9769999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="16" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="23" activeTab="35" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="声光PCA" sheetId="39" r:id="rId1"/>
@@ -24,31 +24,34 @@
     <sheet name="声光迁移MOp" sheetId="28" r:id="rId9"/>
     <sheet name="TransferLowPerformanceHeatmap" sheetId="26" r:id="rId10"/>
     <sheet name="迁移PC光声Top5" sheetId="33" r:id="rId11"/>
-    <sheet name="Fig2C" sheetId="22" r:id="rId12"/>
-    <sheet name="FinalRSPdHeat" sheetId="20" r:id="rId13"/>
-    <sheet name="光声PCA" sheetId="3" r:id="rId14"/>
-    <sheet name="光声最终MOp" sheetId="18" r:id="rId15"/>
-    <sheet name="声光Naive" sheetId="17" r:id="rId16"/>
-    <sheet name="光声迁移命中错失" sheetId="11" r:id="rId17"/>
-    <sheet name="HitMissPie" sheetId="14" r:id="rId18"/>
-    <sheet name="HitMissLinearFitting" sheetId="16" r:id="rId19"/>
-    <sheet name="光声迁移MOp" sheetId="5" r:id="rId20"/>
-    <sheet name="Fig2A" sheetId="6" r:id="rId21"/>
-    <sheet name="声光迁移RSPd" sheetId="8" r:id="rId22"/>
-    <sheet name="光声持续训练" sheetId="24" r:id="rId23"/>
-    <sheet name="光声Naive命中错失" sheetId="9" r:id="rId24"/>
-    <sheet name="Fig1B" sheetId="1" r:id="rId25"/>
-    <sheet name="Fig4D" sheetId="2" r:id="rId26"/>
-    <sheet name="Fig1E" sheetId="4" r:id="rId27"/>
-    <sheet name="Fig1F" sheetId="41" r:id="rId28"/>
-    <sheet name="Fig1GI" sheetId="40" r:id="rId29"/>
-    <sheet name="Fig1H" sheetId="42" r:id="rId30"/>
-    <sheet name="Fig1J" sheetId="43" r:id="rId31"/>
-    <sheet name="Fig1K" sheetId="44" r:id="rId32"/>
-    <sheet name="Fig1L" sheetId="45" r:id="rId33"/>
+    <sheet name="FinalRSPdHeat" sheetId="20" r:id="rId12"/>
+    <sheet name="光声PCA" sheetId="3" r:id="rId13"/>
+    <sheet name="光声最终MOp" sheetId="18" r:id="rId14"/>
+    <sheet name="声光Naive" sheetId="17" r:id="rId15"/>
+    <sheet name="光声迁移命中错失" sheetId="11" r:id="rId16"/>
+    <sheet name="HitMissPie" sheetId="14" r:id="rId17"/>
+    <sheet name="HitMissLinearFitting" sheetId="16" r:id="rId18"/>
+    <sheet name="光声迁移MOp" sheetId="5" r:id="rId19"/>
+    <sheet name="Fig2A" sheetId="6" r:id="rId20"/>
+    <sheet name="声光迁移RSPd" sheetId="8" r:id="rId21"/>
+    <sheet name="光声持续训练" sheetId="24" r:id="rId22"/>
+    <sheet name="光声Naive命中错失" sheetId="9" r:id="rId23"/>
+    <sheet name="Fig1B" sheetId="1" r:id="rId24"/>
+    <sheet name="Fig4D" sheetId="2" r:id="rId25"/>
+    <sheet name="Fig1E" sheetId="4" r:id="rId26"/>
+    <sheet name="Fig1F" sheetId="41" r:id="rId27"/>
+    <sheet name="Fig1GI" sheetId="40" r:id="rId28"/>
+    <sheet name="Fig1H" sheetId="42" r:id="rId29"/>
+    <sheet name="Fig1J" sheetId="43" r:id="rId30"/>
+    <sheet name="Fig1K" sheetId="44" r:id="rId31"/>
+    <sheet name="Fig1L" sheetId="45" r:id="rId32"/>
+    <sheet name="Fig2B12" sheetId="46" r:id="rId33"/>
+    <sheet name="Fig2B3" sheetId="47" r:id="rId34"/>
+    <sheet name="Fig2B4" sheetId="49" r:id="rId35"/>
+    <sheet name="Fig2CD" sheetId="52" r:id="rId36"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">光声PCA!$A$1:$E$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">光声PCA!$A$1:$E$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">声光PCA!$A$1:$E$6</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
@@ -61,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="84">
   <si>
     <t>GroupName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -378,23 +381,23 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>AudioWater_First</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AudioWater_Last</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TrialRI</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>16:20</t>
+    <t>WaterOnly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MOp2/3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MOp5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Layer2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Layer5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -450,7 +453,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -466,6 +469,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1114,108 +1123,6 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A1AD7D0-4CB7-41B7-82F9-51A88A776C7D}">
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="2" width="20.625" customWidth="1"/>
-    <col min="3" max="3" width="10.625" customWidth="1"/>
-    <col min="5" max="5" width="20.625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42D891B7-431D-440C-BC1B-3F6A3C6A425D}">
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -1306,7 +1213,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD9E5BDC-858C-40A4-AAAC-690BD12079BE}">
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -1419,7 +1326,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E1069E3-F224-4C09-B11B-7C6B6BFBA34F}">
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -1512,7 +1419,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7925DD38-417B-4DC2-8355-2344589CB906}">
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -1601,7 +1508,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C64A780-B325-4786-9305-F40760822895}">
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -1698,7 +1605,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50F1590B-8481-4D31-AE83-A1DF5D019A74}">
   <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -1816,7 +1723,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B3020E8-AD0F-478C-8862-BFFD2C6A7D00}">
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -1889,6 +1796,146 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1BB5AC8-8FCA-49B8-AF30-96F469FDC022}">
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="2" width="20.625" customWidth="1"/>
+    <col min="3" max="3" width="10.625" customWidth="1"/>
+    <col min="5" max="5" width="20.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E6" s="1"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1982,16 +2029,15 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1BB5AC8-8FCA-49B8-AF30-96F469FDC022}">
-  <dimension ref="A1:E14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0FF2BA3-B618-4C5A-8B44-5AD472C293A6}">
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="20.625" customWidth="1"/>
-    <col min="3" max="3" width="10.625" customWidth="1"/>
-    <col min="5" max="5" width="20.625" customWidth="1"/>
+    <col min="3" max="4" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2004,115 +2050,48 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>79</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>8</v>
+        <v>79</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E6" s="1"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
+        <v>64</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2122,89 +2101,6 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0FF2BA3-B618-4C5A-8B44-5AD472C293A6}">
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="2" width="20.625" customWidth="1"/>
-    <col min="3" max="4" width="10.625" customWidth="1"/>
-    <col min="5" max="5" width="20.625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E2" s="3"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0E741F2-60D1-4FC1-A219-2E32E5A5D7E0}">
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -2290,7 +2186,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B968D520-F767-413F-A2F7-B05602FB43C8}">
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -2427,7 +2323,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{079BD42A-5F01-4EE5-A8A3-55C6AAB76233}">
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -2523,7 +2419,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -2661,7 +2557,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{955D9409-37EA-42B8-AF2F-C837F3F708A4}">
   <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -2803,7 +2699,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA767627-F2D8-4EE6-BF0E-F5992883EE39}">
   <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -2989,7 +2885,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{673DCBAC-74C8-46D9-9E51-3D79E0C9E0AD}">
   <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -3106,7 +3002,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{394906AA-599F-4A70-9C89-31200372A3CB}">
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -3176,6 +3072,97 @@
         <v>64</v>
       </c>
       <c r="E4" s="1"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8056A83F-BC10-47F4-9E5B-271761E7A9D3}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="20.625" customWidth="1"/>
+    <col min="2" max="2" width="30.625" customWidth="1"/>
+    <col min="3" max="4" width="10.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E4" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3322,97 +3309,6 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8056A83F-BC10-47F4-9E5B-271761E7A9D3}">
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="20.625" customWidth="1"/>
-    <col min="2" max="2" width="30.625" customWidth="1"/>
-    <col min="3" max="4" width="10.625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E2" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E3" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E4" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD36152B-31F8-401F-9C33-F4F4D7D76FD4}">
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -3517,7 +3413,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2493667C-977F-4228-9C57-43128D0072CD}">
   <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -3654,7 +3550,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFFD7975-4DBD-40DC-99B8-46C75232DDD3}">
   <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -3748,6 +3644,230 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41313458-BADF-4857-9285-034C810920CE}">
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="2" width="20.625" customWidth="1"/>
+    <col min="3" max="3" width="10.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="6"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="D2:D3"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A88BD958-BC50-49BD-B351-6193081338D4}">
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="2" width="20.625" customWidth="1"/>
+    <col min="3" max="3" width="10.625" style="5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D3" s="6"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="D2:D3"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D164AAF6-49DE-4601-859D-116EEB8810A4}">
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="2" width="20.625" customWidth="1"/>
+    <col min="3" max="3" width="10.625" style="5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A98ED7B9-5958-4299-B714-06DE861A916E}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="2" width="20.625" customWidth="1"/>
+    <col min="3" max="3" width="10.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C2:C3"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/查询表.xlsx
+++ b/查询表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\张天夫\Documents\MATLAB\Transfer-learning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{102598FF-C6A1-4613-A563-FD5BC9769999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABFCC71B-677B-4B9F-AF9B-F8FCAC4F48A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="23" activeTab="35" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="23" activeTab="36" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="声光PCA" sheetId="39" r:id="rId1"/>
@@ -49,6 +49,7 @@
     <sheet name="Fig2B3" sheetId="47" r:id="rId34"/>
     <sheet name="Fig2B4" sheetId="49" r:id="rId35"/>
     <sheet name="Fig2CD" sheetId="52" r:id="rId36"/>
+    <sheet name="Fig2EF" sheetId="57" r:id="rId37"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">光声PCA!$A$1:$E$6</definedName>
@@ -64,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="84">
   <si>
     <t>GroupName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3823,11 +3824,11 @@
 
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A98ED7B9-5958-4299-B714-06DE861A916E}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="20.625" customWidth="1"/>
-    <col min="3" max="3" width="10.625" customWidth="1"/>
+    <col min="3" max="3" width="10.625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
@@ -3837,7 +3838,7 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="5" t="s">
         <v>5</v>
       </c>
     </row>
@@ -3861,9 +3862,81 @@
       </c>
       <c r="C3" s="7"/>
     </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="C2:C3"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8938E69-59C6-4367-BB47-169E114B1A8F}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="2" width="20.625" customWidth="1"/>
+    <col min="3" max="3" width="10.625" style="5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="6"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C3:C4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/查询表.xlsx
+++ b/查询表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\张天夫\Documents\MATLAB\Transfer-learning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABFCC71B-677B-4B9F-AF9B-F8FCAC4F48A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF6DC4E4-1337-40D0-B56F-17AEF15CCF0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="23" activeTab="36" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="24" activeTab="37" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="声光PCA" sheetId="39" r:id="rId1"/>
@@ -50,6 +50,7 @@
     <sheet name="Fig2B4" sheetId="49" r:id="rId35"/>
     <sheet name="Fig2CD" sheetId="52" r:id="rId36"/>
     <sheet name="Fig2EF" sheetId="57" r:id="rId37"/>
+    <sheet name="Fig3B" sheetId="60" r:id="rId38"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">光声PCA!$A$1:$E$6</definedName>
@@ -65,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="84">
   <si>
     <t>GroupName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3944,6 +3945,67 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43E4F937-8183-4F30-9F49-10ED1A27092D}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="2" width="20.625" customWidth="1"/>
+    <col min="3" max="3" width="10.625" style="5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="7"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C2:C3"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3139FCB1-A8A2-47FE-8D57-A16129805C91}">
   <dimension ref="A1:F4"/>

--- a/查询表.xlsx
+++ b/查询表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\张天夫\Documents\MATLAB\Transfer-learning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF6DC4E4-1337-40D0-B56F-17AEF15CCF0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10DF49B4-362F-4AA3-A215-42639DCC179B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="24" activeTab="37" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="25" activeTab="37" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="声光PCA" sheetId="39" r:id="rId1"/>
@@ -50,7 +50,8 @@
     <sheet name="Fig2B4" sheetId="49" r:id="rId35"/>
     <sheet name="Fig2CD" sheetId="52" r:id="rId36"/>
     <sheet name="Fig2EF" sheetId="57" r:id="rId37"/>
-    <sheet name="Fig3B" sheetId="60" r:id="rId38"/>
+    <sheet name="FlareNtatsHeatmap" sheetId="61" r:id="rId38"/>
+    <sheet name="Fig3B" sheetId="60" r:id="rId39"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">光声PCA!$A$1:$E$6</definedName>
@@ -61,12 +62,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="91">
   <si>
     <t>GroupName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -401,6 +405,27 @@
   <si>
     <t>Layer5</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GroupName</t>
+  </si>
+  <si>
+    <t>Phase</t>
+  </si>
+  <si>
+    <t>Stimulus</t>
+  </si>
+  <si>
+    <t>Learned</t>
+  </si>
+  <si>
+    <t>AudioWater</t>
+  </si>
+  <si>
+    <t>Transfer</t>
+  </si>
+  <si>
+    <t>LightWater</t>
   </si>
 </sst>
 </file>
@@ -3946,6 +3971,50 @@
 </file>
 
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E34FB4E0-A6B3-4D3E-9F14-76476E291129}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43E4F937-8183-4F30-9F49-10ED1A27092D}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
